--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,8 +1020,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B219"/>
+  <dimension ref="A1:C219"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col width="8" customWidth="1" style="2" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1034,6 +1037,11 @@
           <t>commen</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>fault</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1046,8 +1054,12 @@
           <t>string</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
@@ -1059,20 +1071,12 @@
           <t>design</t>
         </is>
       </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>server</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
@@ -1115,6 +1119,9 @@
           <t>表数据错误</t>
         </is>
       </c>
+      <c r="C21" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
@@ -1127,6 +1134,9 @@
           <t>服务不可用</t>
         </is>
       </c>
+      <c r="C22" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
@@ -1139,6 +1149,9 @@
           <t>未找到实体</t>
         </is>
       </c>
+      <c r="C23" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
@@ -1175,6 +1188,9 @@
           <t>下标超出范围</t>
         </is>
       </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
@@ -1199,6 +1215,9 @@
           <t>该实体已经不存在</t>
         </is>
       </c>
+      <c r="C28" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
@@ -1223,6 +1242,9 @@
           <t>当会话未找到时</t>
         </is>
       </c>
+      <c r="C30" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
@@ -1235,6 +1257,9 @@
           <t>会话玩家未找到</t>
         </is>
       </c>
+      <c r="C31" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
@@ -1283,6 +1308,9 @@
           <t>返回消息解析错误，请检查</t>
         </is>
       </c>
+      <c r="C35" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
@@ -1307,6 +1335,9 @@
           <t>节点未注册成功</t>
         </is>
       </c>
+      <c r="C37" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
@@ -1498,6 +1529,9 @@
           <t>登录未知错误</t>
         </is>
       </c>
+      <c r="C54" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
@@ -1522,6 +1556,9 @@
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr"/>
+      <c r="C57" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1" s="2">
       <c r="A58" s="0" t="inlineStr">
@@ -1530,6 +1567,9 @@
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr"/>
+      <c r="C58" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1" s="2">
       <c r="A59" s="0" t="inlineStr">
@@ -1538,6 +1578,9 @@
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr"/>
+      <c r="C59" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1" s="2">
       <c r="A60" s="0" t="inlineStr">
@@ -1546,6 +1589,9 @@
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr"/>
+      <c r="C60" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1" s="2">
       <c r="A61" s="0" t="inlineStr">
@@ -1554,6 +1600,9 @@
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr"/>
+      <c r="C61" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1" s="2">
       <c r="A62" s="0" t="inlineStr">
@@ -1562,6 +1611,9 @@
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr"/>
+      <c r="C62" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
@@ -1578,6 +1630,9 @@
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr"/>
+      <c r="C64" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
@@ -1586,6 +1641,9 @@
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr"/>
+      <c r="C65" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
@@ -1594,6 +1652,9 @@
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr"/>
+      <c r="C66" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
@@ -1602,6 +1663,9 @@
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr"/>
+      <c r="C67" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
@@ -1610,6 +1674,9 @@
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr"/>
+      <c r="C68" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
@@ -1618,6 +1685,9 @@
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr"/>
+      <c r="C69" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
@@ -1626,6 +1696,9 @@
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr"/>
+      <c r="C70" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1" s="2">
       <c r="A71" s="0" t="inlineStr">
@@ -1677,6 +1750,9 @@
           <t>进入的游戏节点已不可用了</t>
         </is>
       </c>
+      <c r="C75" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
@@ -1737,6 +1813,9 @@
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr"/>
+      <c r="C82" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
@@ -1753,6 +1832,9 @@
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr"/>
+      <c r="C84" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
@@ -1785,6 +1867,9 @@
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr"/>
+      <c r="C88" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
@@ -1801,6 +1886,9 @@
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr"/>
+      <c r="C90" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="inlineStr">
@@ -1809,6 +1897,9 @@
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr"/>
+      <c r="C91" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="inlineStr">
@@ -1841,6 +1932,9 @@
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr"/>
+      <c r="C95" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="inlineStr">
@@ -2031,6 +2125,9 @@
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr"/>
+      <c r="C119" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="inlineStr">
@@ -2086,6 +2183,9 @@
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr"/>
+      <c r="C126" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="inlineStr">
@@ -2323,6 +2423,9 @@
           <t>未找到实体的Transfor组件</t>
         </is>
       </c>
+      <c r="C151" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="inlineStr">
@@ -2510,6 +2613,9 @@
           <t>服务繁忙，请稍后重试</t>
         </is>
       </c>
+      <c r="C169" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="inlineStr">
@@ -2668,6 +2774,7 @@
           <t>服务繁忙，请稍后重试</t>
         </is>
       </c>
+      <c r="C183" s="0" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="0" t="inlineStr">
@@ -2850,12 +2957,12 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="0" t="inlineStr">
         <is>
           <t>MatchNotInScene</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B199" s="0" t="inlineStr">
         <is>
           <t>请先进入场景</t>
         </is>
@@ -2883,187 +2990,187 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="0" t="inlineStr">
         <is>
           <t>//attribute_error base=25000 width=1000</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="0" t="inlineStr">
         <is>
           <t>AttributePoolNotFound</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="0" t="inlineStr">
         <is>
           <t>属性池不存在</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="0" t="inlineStr">
         <is>
           <t>AttributePoolLocked</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="0" t="inlineStr">
         <is>
           <t>该属性池尚未解锁</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="0" t="inlineStr">
         <is>
           <t>AttributeDimensionNotFound</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="0" t="inlineStr">
         <is>
           <t>属性维度不存在</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="0" t="inlineStr">
         <is>
           <t>AttributePointsNotEnough</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="0" t="inlineStr">
         <is>
           <t>剩余点数不足</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="0" t="inlineStr">
         <is>
           <t>AttributePointsCannotDecrease</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="0" t="inlineStr">
         <is>
           <t>已分配的点数不能减少,请使用重置</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="0" t="inlineStr">
         <is>
           <t>AttributeDimensionCapExceeded</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="0" t="inlineStr">
         <is>
           <t>超过单项可分配上限</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="0" t="inlineStr">
         <is>
           <t>AttributeSchemeNotFound</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="0" t="inlineStr">
         <is>
           <t>加点方案不存在</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="0" t="inlineStr">
         <is>
           <t>AttributeSchemeLimitReached</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="0" t="inlineStr">
         <is>
           <t>加点方案数量已达上限</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="0" t="inlineStr">
         <is>
           <t>AttributeSchemeSwitchCooldown</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="0" t="inlineStr">
         <is>
           <t>方案切换冷却中</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="0" t="inlineStr">
         <is>
           <t>AttributeSchemeNameInvalid</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="0" t="inlineStr">
         <is>
           <t>方案名称不合法</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="0" t="inlineStr">
         <is>
           <t>AttributeSchemeAlreadyActive</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="0" t="inlineStr">
         <is>
           <t>已经是当前方案</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="0" t="inlineStr">
         <is>
           <t>AttributeInBattle</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="0" t="inlineStr">
         <is>
           <t>战斗中不能修改属性</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="0" t="inlineStr">
         <is>
           <t>AttributeGoldNotEnough</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="0" t="inlineStr">
         <is>
           <t>金币不足</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="0" t="inlineStr">
         <is>
           <t>AttributeNoAutoPlan</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="0" t="inlineStr">
         <is>
           <t>没有可用的自动加点方案</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="0" t="inlineStr">
         <is>
           <t>AttributeNothingToChange</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="0" t="inlineStr">
         <is>
           <t>属性没有变化</t>
         </is>

--- a/data/tip/Tip.xlsx
+++ b/data/tip/Tip.xlsx
@@ -1020,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C219"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" style="2" min="3" max="3"/>
@@ -3176,6 +3176,221 @@
         </is>
       </c>
     </row>
+    <row r="220"/>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>//pet_error base=26000 width=1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>PetNotFound</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>宝宝不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>PetTableRowMissing</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>宝宝数据已失效,请联系客服</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>PetSlotFull</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>可携带的宝宝数量已达上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0" t="inlineStr">
+        <is>
+          <t>PetOwnerLevelNotEnough</t>
+        </is>
+      </c>
+      <c r="B225" s="0" t="inlineStr">
+        <is>
+          <t>主人等级不足,还不能携带这只宝宝</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>PetAlreadyActive</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>这只宝宝已经在出战中</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>PetNotActive</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>当前没有出战的宝宝</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t>PetSummonCooldown</t>
+        </is>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t>操作太频繁,请稍后再试</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t>PetNameInvalid</t>
+        </is>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t>宝宝名称不合法</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t>PetInBattle</t>
+        </is>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t>战斗中不能操作宝宝</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>PetPointsNotEnough</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>宝宝剩余点数不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>PetPointsCannotDecrease</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>已分配的点数不能减少,请使用洗点</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>PetDimensionCapExceeded</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>超过单项可分配上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0" t="inlineStr">
+        <is>
+          <t>PetDimensionNotFound</t>
+        </is>
+      </c>
+      <c r="B234" s="0" t="inlineStr">
+        <is>
+          <t>宝宝属性维度不存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>PetGoldNotEnough</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>金币不足</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>PetNoAutoPlan</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>没有可用的自动加点方案</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>PetNothingToChange</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t>宝宝属性没有变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>PetIdGenerateFailed</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t>宝宝创建失败,请稍后再试</t>
+        </is>
+      </c>
+      <c r="C238" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
